--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_BachelorV5_PCB10_2026-04-20" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_Bachelor_PCB10_2026-09-16" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="322">
   <si>
     <t>No.</t>
   </si>
@@ -73,973 +73,898 @@
     <t>2</t>
   </si>
   <si>
-    <t>K2-3.6×6.1_SMD</t>
+    <t>SKRKAEE020</t>
   </si>
   <si>
     <t>BOOT,RESET</t>
   </si>
   <si>
-    <t>KEY-SMD_2P-L6.2-W3.6-LS8.0</t>
-  </si>
-  <si>
-    <t>K2-1107ST-A4SW-06</t>
-  </si>
-  <si>
-    <t>C118141</t>
+    <t>SW-SMD_L3.9-W3.0-P4.45</t>
+  </si>
+  <si>
+    <t>ALPSALPINE(阿尔卑斯阿尔派)</t>
+  </si>
+  <si>
+    <t>C115357</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>2.54-1*2P母</t>
+  </si>
+  <si>
+    <t>BRAKE_RESISTOR</t>
+  </si>
+  <si>
+    <t>HDR-TH_2P-P2.54-V-F</t>
+  </si>
+  <si>
+    <t>BOOMELE(博穆精密)</t>
+  </si>
+  <si>
+    <t>C49661</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>22nF</t>
+  </si>
+  <si>
+    <t>C1,C44,C71,C76</t>
+  </si>
+  <si>
+    <t>C0201</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C2,C3,C6,C46</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10nF</t>
+  </si>
+  <si>
+    <t>C4,C42,C73,C77</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C5,C43,C79</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>15uF</t>
+  </si>
+  <si>
+    <t>C7,C62,C63</t>
+  </si>
+  <si>
+    <t>C0402</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>0.1uF</t>
   </si>
   <si>
-    <t>C9,C16,C17,C19,C20</t>
-  </si>
-  <si>
-    <t>C0402</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>C9,C17,C19,C20</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>4.7uF</t>
   </si>
   <si>
-    <t>C10,C24,C37</t>
+    <t>C10,C37,C64</t>
   </si>
   <si>
     <t>C0805</t>
   </si>
   <si>
-    <t>5</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C1206</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>C36,C65</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>0.01uF</t>
+  </si>
+  <si>
+    <t>C41,C66</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>C58</t>
+  </si>
+  <si>
+    <t>GRM155R62A104KE14D</t>
+  </si>
+  <si>
+    <t>muRata(村田)</t>
+  </si>
+  <si>
+    <t>C162178</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>C59</t>
+  </si>
+  <si>
+    <t>C1210</t>
+  </si>
+  <si>
+    <t>GRM32EC72A106KE05L</t>
+  </si>
+  <si>
+    <t>C576517</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>6.8nF</t>
+  </si>
+  <si>
+    <t>C72,C74,C75,C78</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>2.2uF</t>
+  </si>
+  <si>
+    <t>C80</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>1u</t>
   </si>
   <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>C1206</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10nF</t>
-  </si>
-  <si>
-    <t>C25,C36</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1000pF</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>C38</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>C39</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>0.01uF</t>
-  </si>
-  <si>
-    <t>C40,C41</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C42,C43,C46,C56,C57</t>
-  </si>
-  <si>
-    <t>C0201</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>C44,C51,C55</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>22nF</t>
-  </si>
-  <si>
-    <t>C48,C52</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>6.8nF</t>
-  </si>
-  <si>
-    <t>C49,C50,C53,C54</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>C58</t>
-  </si>
-  <si>
-    <t>GRM155R62A104KE14D</t>
-  </si>
-  <si>
-    <t>muRata(村田)</t>
-  </si>
-  <si>
-    <t>C162178</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>C59</t>
-  </si>
-  <si>
-    <t>C1210</t>
-  </si>
-  <si>
-    <t>GRM32EC72A106KE05L</t>
-  </si>
-  <si>
-    <t>C576517</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C60</t>
+    <t>C81</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>47nF</t>
+  </si>
+  <si>
+    <t>C82</t>
   </si>
   <si>
     <t>C0603</t>
   </si>
   <si>
+    <t>0603B473K101NT</t>
+  </si>
+  <si>
+    <t>FH(风华)</t>
+  </si>
+  <si>
+    <t>C43254</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>C83</t>
+  </si>
+  <si>
     <t>GRM188D72A105KE01D</t>
   </si>
   <si>
     <t>C23829972</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>47nF</t>
-  </si>
-  <si>
-    <t>C61</t>
-  </si>
-  <si>
-    <t>0603B473K101NT</t>
-  </si>
-  <si>
-    <t>FH(风华)</t>
-  </si>
-  <si>
-    <t>C43254</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>15uF</t>
-  </si>
-  <si>
-    <t>C62,C63</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
-    <t>HDR-F_2.54_1x3P</t>
-  </si>
-  <si>
-    <t>CANBUS</t>
-  </si>
-  <si>
-    <t>HDR-TH_3P-P2.54-V-F</t>
+    <t>XT30PW-M30.G.Y</t>
+  </si>
+  <si>
+    <t>CN1</t>
+  </si>
+  <si>
+    <t>CONN-TH_XT30PW-M</t>
+  </si>
+  <si>
+    <t>AMASS(艾迈斯)</t>
+  </si>
+  <si>
+    <t>C431092</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>CAP_USB_N,CAP_USB_P</t>
+    <t>MAX40200AUK+T</t>
+  </si>
+  <si>
+    <t>DIODEREG50,DIODEUSB50</t>
+  </si>
+  <si>
+    <t>TSOT-23-5_L2.9-W1.6-P0.95-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>ADI(亚德诺)/MAXIM(美信)</t>
+  </si>
+  <si>
+    <t>C2649430</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>MAX40200AUK+T</t>
-  </si>
-  <si>
-    <t>DIODE33,DIODEREG50,DIODEUSB50</t>
-  </si>
-  <si>
-    <t>TSOT-23-5_L2.9-W1.6-P0.95-LS2.8-BL</t>
-  </si>
-  <si>
-    <t>ADI(亚德诺)/MAXIM(美信)</t>
-  </si>
-  <si>
-    <t>C2649430</t>
+    <t>2.54-1*6P母</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>HDR-TH_6P-P2.54-V-F</t>
+  </si>
+  <si>
+    <t>C40877</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>ESP32-S3-WROOM-1(N16R8)</t>
-  </si>
-  <si>
-    <t>ESP1</t>
-  </si>
-  <si>
-    <t>WIRELM-SMD_ESP32-S3-WROOM-1</t>
-  </si>
-  <si>
-    <t>ESP32-S3-WROOM-1-N16R8</t>
+    <t>INA238AIDGSR</t>
+  </si>
+  <si>
+    <t>INA238</t>
+  </si>
+  <si>
+    <t>VSSOP-10_L3.0-W3.0-P0.50-LS4.9-BL</t>
+  </si>
+  <si>
+    <t>TI(德州仪器)</t>
+  </si>
+  <si>
+    <t>C2868250</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>47uH</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>IND-SMD_L4.1-W4.1_YSMC0430H</t>
+  </si>
+  <si>
+    <t>FTC404030S470MBCA</t>
+  </si>
+  <si>
+    <t>cjiang(长江微电)</t>
+  </si>
+  <si>
+    <t>C53436372</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>KT-0603YG</t>
+  </si>
+  <si>
+    <t>LED33,LED50,LED120</t>
+  </si>
+  <si>
+    <t>LED0603-RD</t>
+  </si>
+  <si>
+    <t>KENTO</t>
+  </si>
+  <si>
+    <t>C2289</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>MID1,MID2,MID3</t>
+  </si>
+  <si>
+    <t>CGA6P1X7R1N106KT0Y0E</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>C5159419</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>CSD88599Q5DC</t>
+  </si>
+  <si>
+    <t>MOSFET_A1,MOSFET_B1,MOSFET_C1</t>
+  </si>
+  <si>
+    <t>SON-22_L5.0-W6.0-P0.50-CSD88599Q5DCT</t>
+  </si>
+  <si>
+    <t>C2871380</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>WJ128V-5.0-3P</t>
+  </si>
+  <si>
+    <t>MOTOR_TERMINAL2</t>
+  </si>
+  <si>
+    <t>CONN-TH_3P-P5.00_WJ128V-5.0-3P</t>
+  </si>
+  <si>
+    <t>WJ128V-5.0-03P-14-00A</t>
+  </si>
+  <si>
+    <t>KANGNEX(康奈克斯电气)</t>
+  </si>
+  <si>
+    <t>C8270</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>AGM60P30AP</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>PDFN-8_L3.3-W3.3-P0.65-BL</t>
+  </si>
+  <si>
+    <t>AGMSEMI(芯控源)</t>
+  </si>
+  <si>
+    <t>C20625923</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>169K</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>4.7kΩ</t>
+  </si>
+  <si>
+    <t>R2,R5,R6</t>
+  </si>
+  <si>
+    <t>R0201</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>330Ω</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>R4,R14</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>5.1kΩ</t>
+  </si>
+  <si>
+    <t>R7,R8</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>R12,R13,R36,R86,R127,R128</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>100kΩ</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>12.4kΩ</t>
+  </si>
+  <si>
+    <t>R37,R85</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>15K</t>
+  </si>
+  <si>
+    <t>R45</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>R46</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>402K</t>
+  </si>
+  <si>
+    <t>R47</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>110Ω</t>
+  </si>
+  <si>
+    <t>R48</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>R98,R99,R100,R101</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>33R</t>
+  </si>
+  <si>
+    <t>R102,R104,R107,R110,R111,R112,R113,R118</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>49.9R</t>
+  </si>
+  <si>
+    <t>R103,R105,R108,R109,R114,R115,R117</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>10R</t>
+  </si>
+  <si>
+    <t>R106,R116</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>50kΩ</t>
+  </si>
+  <si>
+    <t>R125,R126</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>1mΩ</t>
+  </si>
+  <si>
+    <t>R135,R136,R137</t>
+  </si>
+  <si>
+    <t>R2512</t>
+  </si>
+  <si>
+    <t>ECSR2512FR001K9</t>
+  </si>
+  <si>
+    <t>RESI(开步睿思)</t>
+  </si>
+  <si>
+    <t>C349181</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>LM5161PWPR</t>
+  </si>
+  <si>
+    <t>REG50</t>
+  </si>
+  <si>
+    <t>HTSSOP-14_L5.0-W4.4-P0.65-LS6.4-BL-EP3.0</t>
+  </si>
+  <si>
+    <t>C468246</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>HR911205C</t>
+  </si>
+  <si>
+    <t>RJ5</t>
+  </si>
+  <si>
+    <t>RJ45-TH_HR911205C</t>
+  </si>
+  <si>
+    <t>HANRUN(汉仁)</t>
+  </si>
+  <si>
+    <t>C191736</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>2mΩ</t>
+  </si>
+  <si>
+    <t>SHUNTPWR</t>
+  </si>
+  <si>
+    <t>LR2512-23R002F4</t>
+  </si>
+  <si>
+    <t>RALEC(旺诠)</t>
+  </si>
+  <si>
+    <t>C154685</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>AGM12N10AP</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>C17701055</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>UCC27511ADBVR</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.9-BL</t>
+  </si>
+  <si>
+    <t>C2676982</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>LM5160QPWPRQ1</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>C524318</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>W5500</t>
+  </si>
+  <si>
+    <t>U4,U15</t>
+  </si>
+  <si>
+    <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
+  </si>
+  <si>
+    <t>WIZNET</t>
+  </si>
+  <si>
+    <t>C32843</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>LSM6DSOWTR</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>LGA-14L_L3.0-W2.5-P0.50-TL</t>
+  </si>
+  <si>
+    <t>ST(意法半导体)</t>
+  </si>
+  <si>
+    <t>C2829074</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>LM75AD,118</t>
+  </si>
+  <si>
+    <t>U11</t>
+  </si>
+  <si>
+    <t>SOIC-8_L5.0-W4.0-P1.27-LS6.0-BL</t>
+  </si>
+  <si>
+    <t>NXP(恩智浦)</t>
+  </si>
+  <si>
+    <t>C7963</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>AS5047P-ATSM</t>
+  </si>
+  <si>
+    <t>U13</t>
+  </si>
+  <si>
+    <t>TSSOP-14_L5.0-W4.4-P0.65-LS6.4-BL</t>
+  </si>
+  <si>
+    <t>ams(艾迈斯半导体)</t>
+  </si>
+  <si>
+    <t>C962063</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>68uH</t>
+  </si>
+  <si>
+    <t>U14</t>
+  </si>
+  <si>
+    <t>IND-SMD_L7.2-W6.6_GPSR07X0</t>
+  </si>
+  <si>
+    <t>CYA0650-68UH</t>
+  </si>
+  <si>
+    <t>SHOU HAN(首韩)</t>
+  </si>
+  <si>
+    <t>C5189964</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>TLV76733DRVR</t>
+  </si>
+  <si>
+    <t>U16</t>
+  </si>
+  <si>
+    <t>WSON-6_L2.0-W2.0-P0.65-TL-EP</t>
+  </si>
+  <si>
+    <t>C2848334</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>DRV8320SRTVR</t>
+  </si>
+  <si>
+    <t>U18</t>
+  </si>
+  <si>
+    <t>WQFN-32_L5.0-W5.0-P0.50-TL-EP3.5</t>
+  </si>
+  <si>
+    <t>C2653535</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>INA241A3IDDFR</t>
+  </si>
+  <si>
+    <t>U21,U22,U23</t>
+  </si>
+  <si>
+    <t>SOT-23-8_L2.9-W1.6-P0.65-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>C6051860</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>2.4GHz</t>
+  </si>
+  <si>
+    <t>U24</t>
+  </si>
+  <si>
+    <t>WIRELM-SMD_ESP32-S3-WROOM-1U</t>
+  </si>
+  <si>
+    <t>ESP32-S3-WROOM-1U-N16R8</t>
   </si>
   <si>
     <t>ESPRESSIF(乐鑫)</t>
   </si>
   <si>
-    <t>C2913202</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>HDR-F-2.54_1x4</t>
-  </si>
-  <si>
-    <t>I2C,UART</t>
-  </si>
-  <si>
-    <t>HDR-F-2.54_1X4</t>
-  </si>
-  <si>
-    <t>C225501</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>INA238AIDGSR</t>
-  </si>
-  <si>
-    <t>INA238</t>
-  </si>
-  <si>
-    <t>VSSOP-10_L3.0-W3.0-P0.50-LS4.9-BL</t>
-  </si>
-  <si>
-    <t>TI(德州仪器)</t>
-  </si>
-  <si>
-    <t>C2868250</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>HR911105A</t>
-  </si>
-  <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>RJ45-TH_HR911105A</t>
-  </si>
-  <si>
-    <t>HANRUN(汉仁)</t>
-  </si>
-  <si>
-    <t>C12074</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>HX1188NLT</t>
-  </si>
-  <si>
-    <t>L4</t>
-  </si>
-  <si>
-    <t>RJ45-SMD_HX1188NLT</t>
-  </si>
-  <si>
-    <t>PULSE(普思)</t>
-  </si>
-  <si>
-    <t>C9363</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>KT-0603Y</t>
-  </si>
-  <si>
-    <t>LED1,LED2,LED3</t>
-  </si>
-  <si>
-    <t>LED0603-R-RD</t>
-  </si>
-  <si>
-    <t>KENTO</t>
-  </si>
-  <si>
-    <t>C2287</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>KT-0603YG</t>
-  </si>
-  <si>
-    <t>LED33,LED50</t>
-  </si>
-  <si>
-    <t>LED0603-RD</t>
-  </si>
-  <si>
-    <t>C2289</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2.54-1*2P母</t>
-  </si>
-  <si>
-    <t>MCP_INT</t>
-  </si>
-  <si>
-    <t>HDR-TH_2P-P2.54-V-F</t>
-  </si>
-  <si>
-    <t>BOOMELE(博穆精密)</t>
-  </si>
-  <si>
-    <t>C49661</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>TF-01A</t>
-  </si>
-  <si>
-    <t>MICRO-SD</t>
-  </si>
-  <si>
-    <t>TF-SMD_TF-01A</t>
-  </si>
-  <si>
-    <t>韩国韩荣</t>
-  </si>
-  <si>
-    <t>C91145</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>MID1,MID2,MID3</t>
-  </si>
-  <si>
-    <t>CGA6P1X7R1N106KT0Y0E</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>C5159419</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>CSD88599Q5DC</t>
-  </si>
-  <si>
-    <t>MOSFET_A,MOSFET_B,MOSFET_C</t>
-  </si>
-  <si>
-    <t>SON-22_L5.0-W6.0-P0.50-CSD88599Q5DCT</t>
-  </si>
-  <si>
-    <t>C2871380</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>DRV8323SRTAR</t>
-  </si>
-  <si>
-    <t>MOTOR_DRV1</t>
-  </si>
-  <si>
-    <t>WQFN-40_L6.0-W6.0-P0.50-TL-EP4.5</t>
-  </si>
-  <si>
-    <t>C701784</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>WJ128V-5.0-3P</t>
-  </si>
-  <si>
-    <t>MOTOR_TERMINAL1</t>
-  </si>
-  <si>
-    <t>CONN-TH_3P-P5.00_WJ128V-5.0-3P</t>
-  </si>
-  <si>
-    <t>WJ128V-5.0-03P-14-00A</t>
-  </si>
-  <si>
-    <t>KANGNEX(康奈克斯电气)</t>
-  </si>
-  <si>
-    <t>C8270</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>2.54-1*4P母</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>HDR-TH_4P-P2.54-V-F</t>
-  </si>
-  <si>
-    <t>C2718488</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>XT60PW-M</t>
-  </si>
-  <si>
-    <t>PWR</t>
-  </si>
-  <si>
-    <t>CONN-TH_XT60PW-M</t>
-  </si>
-  <si>
-    <t>AMASS(艾迈斯)</t>
-  </si>
-  <si>
-    <t>C98732</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>4.7kΩ</t>
-  </si>
-  <si>
-    <t>R2,R5,R6</t>
-  </si>
-  <si>
-    <t>R0201</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>330Ω</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>5.1kΩ</t>
-  </si>
-  <si>
-    <t>R7,R8</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>50kΩ</t>
-  </si>
-  <si>
-    <t>R9,R10</t>
-  </si>
-  <si>
-    <t>R0402</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>0Ω</t>
-  </si>
-  <si>
-    <t>R11,R14</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>R12,R13,R19,R36,R38</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>100kΩ</t>
-  </si>
-  <si>
-    <t>R16</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>12.4kΩ</t>
-  </si>
-  <si>
-    <t>R18,R37</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>75Ω</t>
-  </si>
-  <si>
-    <t>R28,R29,R30,R31</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>3.5mΩ</t>
-  </si>
-  <si>
-    <t>R41,R42,R43,SHUNTPWR</t>
-  </si>
-  <si>
-    <t>RES-SMD_L6.4-W3.2-R2512</t>
-  </si>
-  <si>
-    <t>LRBN25GFER0035S</t>
-  </si>
-  <si>
-    <t>NCT(利昇达)</t>
-  </si>
-  <si>
-    <t>C5121063</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>15K</t>
-  </si>
-  <si>
-    <t>R45</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>R46,R80,R81</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
-    <t>R47</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>110Ω</t>
-  </si>
-  <si>
-    <t>R48</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>49.9R</t>
-  </si>
-  <si>
-    <t>R57,R58,R66,R67</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>10R</t>
-  </si>
-  <si>
-    <t>R59,R68</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>33R</t>
-  </si>
-  <si>
-    <t>R60,R61,R62,R63,R69,R70,R71,R72</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>82R</t>
-  </si>
-  <si>
-    <t>R64,R65,R73,R74</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>R75,R76,R77,R78</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>200K</t>
-  </si>
-  <si>
-    <t>R79</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>R82,R83,R84</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>AMS1117-3.3</t>
-  </si>
-  <si>
-    <t>REG33</t>
-  </si>
-  <si>
-    <t>SOT-223-3_L6.5-W3.4-P2.30-LS7.0-BR</t>
-  </si>
-  <si>
-    <t>AMS</t>
-  </si>
-  <si>
-    <t>C6186</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>LM5161PWPR</t>
-  </si>
-  <si>
-    <t>REG50</t>
-  </si>
-  <si>
-    <t>HTSSOP-14_L5.0-W4.4-P0.65-LS6.4-BL-EP3.0</t>
-  </si>
-  <si>
-    <t>C468246</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>R-RJ45R08P-C000</t>
-  </si>
-  <si>
-    <t>RJ2</t>
-  </si>
-  <si>
-    <t>RJ45-TH_R-RJ45R08P-C000</t>
-  </si>
-  <si>
-    <t>Ckmtw(灿科盟)</t>
-  </si>
-  <si>
-    <t>C386757</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>SQD50P06-15L_GE3</t>
-  </si>
-  <si>
-    <t>RPPMOSFET</t>
-  </si>
-  <si>
-    <t>TO-252-2_L6.6-W6.1-P4.58-LS9.9-BR</t>
-  </si>
-  <si>
-    <t>VISHAY(威世)</t>
-  </si>
-  <si>
-    <t>C3281500</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>DSHP02TSGET</t>
-  </si>
-  <si>
-    <t>SW1</t>
-  </si>
-  <si>
-    <t>SW-SMD_4P_DSHP02TSGET</t>
-  </si>
-  <si>
-    <t>YE</t>
-  </si>
-  <si>
-    <t>C40735</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>MCP23017-E/SO</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>SOIC-28_L18.0-W7.5-P1.27-LS10.3-BL</t>
-  </si>
-  <si>
-    <t>MICROCHIP(美国微芯)</t>
-  </si>
-  <si>
-    <t>C47023</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>W5500</t>
-  </si>
-  <si>
-    <t>U3,U4</t>
-  </si>
-  <si>
-    <t>LQFP-48_L7.0-W7.0-P0.50-LS9.0-BL</t>
-  </si>
-  <si>
-    <t>WIZNET</t>
-  </si>
-  <si>
-    <t>C32843</t>
+    <t>C3013946</t>
   </si>
   <si>
     <t>69</t>
   </si>
   <si>
-    <t>SN65HVD230DR</t>
-  </si>
-  <si>
-    <t>U10</t>
-  </si>
-  <si>
-    <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
-    <t>C12084</t>
+    <t>TYPE-C16PIN</t>
+  </si>
+  <si>
+    <t>USB1</t>
+  </si>
+  <si>
+    <t>USB-C-SMD_TYPE-C16PIN</t>
+  </si>
+  <si>
+    <t>C393939</t>
   </si>
   <si>
     <t>70</t>
   </si>
   <si>
-    <t>LM75AD,118</t>
-  </si>
-  <si>
-    <t>U11</t>
-  </si>
-  <si>
-    <t>SOIC-8_L5.0-W4.0-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
-    <t>NXP(恩智浦)</t>
-  </si>
-  <si>
-    <t>C7963</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>LSM6DSOWTR</t>
-  </si>
-  <si>
-    <t>U12</t>
-  </si>
-  <si>
-    <t>LGA-14L_L3.0-W2.5-P0.50-TL</t>
-  </si>
-  <si>
-    <t>ST(意法半导体)</t>
-  </si>
-  <si>
-    <t>C2829074</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>AS5047P-ATSM</t>
-  </si>
-  <si>
-    <t>U13</t>
-  </si>
-  <si>
-    <t>TSSOP-14_L5.0-W4.4-P0.65-LS6.4-BL</t>
-  </si>
-  <si>
-    <t>ams(艾迈斯半导体)</t>
-  </si>
-  <si>
-    <t>C962063</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>68uH</t>
-  </si>
-  <si>
-    <t>U14</t>
-  </si>
-  <si>
-    <t>IND-SMD_L7.2-W6.6_GPSR07X0</t>
-  </si>
-  <si>
-    <t>CYA0650-68UH</t>
-  </si>
-  <si>
-    <t>SHOU HAN(首韩)</t>
-  </si>
-  <si>
-    <t>C5189964</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>TYPE-C16PIN</t>
-  </si>
-  <si>
-    <t>USB1</t>
-  </si>
-  <si>
-    <t>USB-C-SMD_TYPE-C16PIN</t>
-  </si>
-  <si>
-    <t>C393939</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
     <t>25MHz</t>
   </si>
   <si>
-    <t>X3,X4</t>
+    <t>X4,X5</t>
   </si>
   <si>
     <t>OSC-SMD_4P-L2.5-W2.0-BL</t>
@@ -1428,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -1518,10 +1443,10 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
         <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
       </c>
       <c r="I3" t="s">
         <v>24</v>
@@ -1535,7 +1460,7 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -1550,36 +1475,36 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
         <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
@@ -1596,22 +1521,22 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
         <v>14</v>
@@ -1628,22 +1553,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
         <v>39</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
       </c>
       <c r="G7" t="s">
         <v>14</v>
@@ -1660,22 +1585,22 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
         <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
       </c>
       <c r="G8" t="s">
         <v>14</v>
@@ -1692,22 +1617,22 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
         <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
       </c>
       <c r="G9" t="s">
         <v>14</v>
@@ -1724,19 +1649,19 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
         <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
@@ -1756,22 +1681,22 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
         <v>14</v>
@@ -1788,22 +1713,22 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
         <v>14</v>
@@ -1820,22 +1745,22 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" t="s">
         <v>54</v>
       </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
         <v>14</v>
@@ -1852,22 +1777,22 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s">
         <v>14</v>
@@ -1884,22 +1809,22 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
         <v>14</v>
@@ -1916,191 +1841,191 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="J16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="J17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="I18" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="I19" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="I20" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="J20" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J21" t="s">
         <v>18</v>
@@ -2108,127 +2033,127 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="J22" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E23" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="F24" t="s">
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="J24" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H25" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="I25" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J25" t="s">
         <v>18</v>
@@ -2236,31 +2161,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H26" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="I26" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="J26" t="s">
         <v>18</v>
@@ -2268,31 +2193,31 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="I27" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="J27" t="s">
         <v>18</v>
@@ -2300,31 +2225,31 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="H28" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I28" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J28" t="s">
         <v>18</v>
@@ -2332,31 +2257,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E29" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H29" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I29" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J29" t="s">
         <v>18</v>
@@ -2364,31 +2289,31 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E30" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H30" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="I30" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="J30" t="s">
         <v>18</v>
@@ -2396,31 +2321,31 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E31" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H31" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="I31" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="J31" t="s">
         <v>18</v>
@@ -2428,31 +2353,31 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E32" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H32" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="I32" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J32" t="s">
         <v>18</v>
@@ -2460,275 +2385,275 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E33" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>157</v>
       </c>
       <c r="G33" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="I33" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="J33" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E34" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>157</v>
+        <v>14</v>
       </c>
       <c r="I34" t="s">
-        <v>158</v>
+        <v>14</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E35" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>161</v>
+        <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="I35" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="J35" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="G36" t="s">
-        <v>165</v>
+        <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>122</v>
+        <v>14</v>
       </c>
       <c r="I36" t="s">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="J36" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>170</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>122</v>
+        <v>14</v>
       </c>
       <c r="I37" t="s">
-        <v>173</v>
+        <v>14</v>
       </c>
       <c r="J37" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>173</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
         <v>174</v>
       </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>175</v>
       </c>
-      <c r="D38" t="s">
-        <v>176</v>
-      </c>
       <c r="E38" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="G38" t="s">
-        <v>178</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="I38" t="s">
-        <v>180</v>
+        <v>14</v>
       </c>
       <c r="J38" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>182</v>
+        <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E39" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="G39" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="I39" t="s">
-        <v>185</v>
+        <v>14</v>
       </c>
       <c r="J39" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D40" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E40" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="G40" t="s">
-        <v>187</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="I40" t="s">
-        <v>191</v>
+        <v>14</v>
       </c>
       <c r="J40" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D41" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="E41" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
@@ -2748,19 +2673,19 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
@@ -2780,19 +2705,19 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D43" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E43" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
@@ -2812,19 +2737,19 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B44">
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D44" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E44" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
@@ -2844,22 +2769,22 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D45" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="E45" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F45" t="s">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="G45" t="s">
         <v>14</v>
@@ -2876,22 +2801,22 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="D46" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="E46" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="G46" t="s">
         <v>14</v>
@@ -2908,22 +2833,22 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D47" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="E47" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>199</v>
       </c>
       <c r="G47" t="s">
         <v>14</v>
@@ -2940,19 +2865,19 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D48" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="E48" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
@@ -2972,22 +2897,22 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="D49" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="E49" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
+        <v>205</v>
       </c>
       <c r="G49" t="s">
         <v>14</v>
@@ -3004,22 +2929,22 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D50" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="E50" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F50" t="s">
-        <v>14</v>
+        <v>208</v>
       </c>
       <c r="G50" t="s">
         <v>14</v>
@@ -3036,54 +2961,54 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C51" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D51" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="E51" t="s">
-        <v>227</v>
+        <v>163</v>
       </c>
       <c r="F51" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="G51" t="s">
-        <v>228</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>229</v>
+        <v>14</v>
       </c>
       <c r="I51" t="s">
-        <v>230</v>
+        <v>14</v>
       </c>
       <c r="J51" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D52" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="E52" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="F52" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="G52" t="s">
         <v>14</v>
@@ -3100,22 +3025,22 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="D53" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="E53" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="F53" t="s">
-        <v>235</v>
+        <v>14</v>
       </c>
       <c r="G53" t="s">
         <v>14</v>
@@ -3132,319 +3057,319 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="D54" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="E54" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="F54" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="G54" t="s">
-        <v>14</v>
+        <v>224</v>
       </c>
       <c r="H54" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="I54" t="s">
-        <v>14</v>
+        <v>226</v>
       </c>
       <c r="J54" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D55" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E55" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="H55" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="I55" t="s">
-        <v>14</v>
+        <v>231</v>
       </c>
       <c r="J55" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D56" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="E56" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="F56" t="s">
-        <v>244</v>
+        <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>14</v>
+        <v>233</v>
       </c>
       <c r="H56" t="s">
-        <v>14</v>
+        <v>236</v>
       </c>
       <c r="I56" t="s">
-        <v>14</v>
+        <v>237</v>
       </c>
       <c r="J56" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D57" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E57" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="F57" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="G57" t="s">
-        <v>14</v>
+        <v>241</v>
       </c>
       <c r="H57" t="s">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="I57" t="s">
-        <v>14</v>
+        <v>243</v>
       </c>
       <c r="J57" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B58">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D58" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E58" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="F58" t="s">
-        <v>250</v>
+        <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>14</v>
+        <v>245</v>
       </c>
       <c r="H58" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="I58" t="s">
-        <v>14</v>
+        <v>247</v>
       </c>
       <c r="J58" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>248</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>249</v>
+      </c>
+      <c r="D59" t="s">
+        <v>250</v>
+      </c>
+      <c r="E59" t="s">
+        <v>251</v>
+      </c>
+      <c r="F59" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" t="s">
+        <v>249</v>
+      </c>
+      <c r="H59" t="s">
+        <v>118</v>
+      </c>
+      <c r="I59" t="s">
         <v>252</v>
       </c>
-      <c r="B59">
-        <v>4</v>
-      </c>
-      <c r="C59" t="s">
-        <v>253</v>
-      </c>
-      <c r="D59" t="s">
-        <v>254</v>
-      </c>
-      <c r="E59" t="s">
-        <v>195</v>
-      </c>
-      <c r="F59" t="s">
-        <v>253</v>
-      </c>
-      <c r="G59" t="s">
-        <v>14</v>
-      </c>
-      <c r="H59" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59" t="s">
-        <v>14</v>
-      </c>
       <c r="J59" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>253</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>254</v>
+      </c>
+      <c r="D60" t="s">
         <v>255</v>
       </c>
-      <c r="B60">
-        <v>4</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="E60" t="s">
+        <v>230</v>
+      </c>
+      <c r="F60" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>254</v>
+      </c>
+      <c r="H60" t="s">
+        <v>118</v>
+      </c>
+      <c r="I60" t="s">
         <v>256</v>
       </c>
-      <c r="D60" t="s">
-        <v>257</v>
-      </c>
-      <c r="E60" t="s">
-        <v>195</v>
-      </c>
-      <c r="F60" t="s">
-        <v>256</v>
-      </c>
-      <c r="G60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60" t="s">
-        <v>14</v>
-      </c>
       <c r="J60" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>257</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
         <v>258</v>
       </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>259</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>260</v>
       </c>
-      <c r="E61" t="s">
-        <v>195</v>
-      </c>
       <c r="F61" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>14</v>
+        <v>258</v>
       </c>
       <c r="H61" t="s">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="I61" t="s">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="J61" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E62" t="s">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="F62" t="s">
-        <v>262</v>
+        <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>14</v>
+        <v>264</v>
       </c>
       <c r="H62" t="s">
-        <v>14</v>
+        <v>267</v>
       </c>
       <c r="I62" t="s">
-        <v>14</v>
+        <v>268</v>
       </c>
       <c r="J62" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D63" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E63" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
       </c>
       <c r="G63" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H63" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I63" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="J63" t="s">
         <v>18</v>
@@ -3452,31 +3377,31 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D64" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E64" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H64" t="s">
-        <v>122</v>
+        <v>279</v>
       </c>
       <c r="I64" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="J64" t="s">
         <v>18</v>
@@ -3484,31 +3409,31 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D65" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E65" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F65" t="s">
-        <v>14</v>
+        <v>282</v>
       </c>
       <c r="G65" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="H65" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="I65" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="J65" t="s">
         <v>18</v>
@@ -3516,31 +3441,31 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D66" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E66" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="F66" t="s">
         <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="H66" t="s">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="I66" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="J66" t="s">
         <v>18</v>
@@ -3548,31 +3473,31 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D67" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E67" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="H67" t="s">
-        <v>291</v>
+        <v>118</v>
       </c>
       <c r="I67" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="J67" t="s">
         <v>18</v>
@@ -3580,31 +3505,31 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D68" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E68" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="H68" t="s">
-        <v>297</v>
+        <v>118</v>
       </c>
       <c r="I68" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J68" t="s">
         <v>18</v>
@@ -3612,31 +3537,31 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D69" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E69" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F69" t="s">
-        <v>14</v>
+        <v>304</v>
       </c>
       <c r="G69" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="H69" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="I69" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="J69" t="s">
         <v>18</v>
@@ -3644,31 +3569,31 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D70" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E70" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H70" t="s">
-        <v>122</v>
+        <v>286</v>
       </c>
       <c r="I70" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="J70" t="s">
         <v>18</v>
@@ -3676,198 +3601,38 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D71" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E71" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F71" t="s">
-        <v>14</v>
+        <v>316</v>
       </c>
       <c r="G71" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="H71" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I71" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="J71" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>316</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72" t="s">
-        <v>317</v>
-      </c>
-      <c r="D72" t="s">
-        <v>318</v>
-      </c>
-      <c r="E72" t="s">
-        <v>319</v>
-      </c>
-      <c r="F72" t="s">
-        <v>14</v>
-      </c>
-      <c r="G72" t="s">
-        <v>317</v>
-      </c>
-      <c r="H72" t="s">
-        <v>320</v>
-      </c>
-      <c r="I72" t="s">
-        <v>321</v>
-      </c>
-      <c r="J72" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>322</v>
-      </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73" t="s">
-        <v>323</v>
-      </c>
-      <c r="D73" t="s">
-        <v>324</v>
-      </c>
-      <c r="E73" t="s">
-        <v>325</v>
-      </c>
-      <c r="F73" t="s">
-        <v>14</v>
-      </c>
-      <c r="G73" t="s">
-        <v>323</v>
-      </c>
-      <c r="H73" t="s">
-        <v>326</v>
-      </c>
-      <c r="I73" t="s">
-        <v>327</v>
-      </c>
-      <c r="J73" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>328</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74" t="s">
-        <v>329</v>
-      </c>
-      <c r="D74" t="s">
-        <v>330</v>
-      </c>
-      <c r="E74" t="s">
-        <v>331</v>
-      </c>
-      <c r="F74" t="s">
-        <v>329</v>
-      </c>
-      <c r="G74" t="s">
-        <v>332</v>
-      </c>
-      <c r="H74" t="s">
-        <v>333</v>
-      </c>
-      <c r="I74" t="s">
-        <v>334</v>
-      </c>
-      <c r="J74" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>335</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-      <c r="C75" t="s">
-        <v>336</v>
-      </c>
-      <c r="D75" t="s">
-        <v>337</v>
-      </c>
-      <c r="E75" t="s">
-        <v>338</v>
-      </c>
-      <c r="F75" t="s">
-        <v>14</v>
-      </c>
-      <c r="G75" t="s">
-        <v>336</v>
-      </c>
-      <c r="H75" t="s">
-        <v>333</v>
-      </c>
-      <c r="I75" t="s">
-        <v>339</v>
-      </c>
-      <c r="J75" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>340</v>
-      </c>
-      <c r="B76">
-        <v>2</v>
-      </c>
-      <c r="C76" t="s">
-        <v>341</v>
-      </c>
-      <c r="D76" t="s">
-        <v>342</v>
-      </c>
-      <c r="E76" t="s">
-        <v>343</v>
-      </c>
-      <c r="F76" t="s">
-        <v>341</v>
-      </c>
-      <c r="G76" t="s">
-        <v>344</v>
-      </c>
-      <c r="H76" t="s">
-        <v>345</v>
-      </c>
-      <c r="I76" t="s">
-        <v>346</v>
-      </c>
-      <c r="J76" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
         <v>14</v>
       </c>
     </row>
